--- a/data/b2_centro/B2 Centro 04-2026.xlsx
+++ b/data/b2_centro/B2 Centro 04-2026.xlsx
@@ -4802,29 +4802,29 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>3471.68</v>
+        <v>1913.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>2146.88</v>
+        <v>79005.39</v>
       </c>
     </row>
     <row r="4">
@@ -4833,142 +4833,142 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>79397.53999999999</v>
+        <v>3936.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>2013.29</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4188.11</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>38000</v>
+        <v>5435.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46122</v>
+        <v>46124</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4300</v>
+        <v>1614.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Limpeza da caixa separadora</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>5778.48</v>
+        <v>4161.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>1962.32</v>
+        <v>12860.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1938.72</v>
+        <v>3306.29</v>
       </c>
     </row>
     <row r="12">
@@ -4977,88 +4977,88 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>12968.91</v>
+        <v>1043.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>4775.26</v>
+        <v>5282.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1373.64</v>
+        <v>27699.46</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46131</v>
+        <v>46134</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>5283.36</v>
+        <v>1424.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>46132</v>
+        <v>46137</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>27833.63</v>
+        <v>2153.39</v>
       </c>
     </row>
     <row r="17">
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5478.58</v>
+        <v>5758.79</v>
       </c>
     </row>
     <row r="18">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2885.69</v>
+        <v>3092.15</v>
       </c>
     </row>
   </sheetData>
